--- a/Free rooms Mar26.xlsx
+++ b/Free rooms Mar26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ad.sast.org.uk\redirected-user-files\SHAStaffRedirectedFiles\Staff\Kate.BOTTERILL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA33F08E-38D4-4B8A-8D21-1603A16B3FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C6C209-67F4-4E50-A46A-0381E8CCFE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{48014A31-AD53-4B67-A04D-85E73C5C3F8A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="79">
   <si>
     <t>Room</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>B1</t>
-  </si>
-  <si>
-    <t>B11</t>
   </si>
   <si>
     <t>B12</t>
@@ -370,21 +367,21 @@
   <dxfs count="2">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -718,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE3051D-A1AC-464E-9652-A9E1F2B85FA2}">
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -730,154 +727,154 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="AY1" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.3">
@@ -1982,13 +1979,13 @@
         <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>3</v>
@@ -2003,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>3</v>
@@ -2015,19 +2012,19 @@
         <v>3</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V9" s="4" t="s">
         <v>3</v>
@@ -2048,7 +2045,7 @@
         <v>3</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="4" t="s">
         <v>3</v>
@@ -2060,25 +2057,25 @@
         <v>3</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AK9" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM9" s="4" t="s">
         <v>3</v>
@@ -2125,7 +2122,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
@@ -2134,7 +2131,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>2</v>
@@ -2146,19 +2143,19 @@
         <v>3</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>3</v>
@@ -2167,13 +2164,13 @@
         <v>3</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" s="4" t="s">
         <v>3</v>
@@ -2182,7 +2179,7 @@
         <v>2</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10" s="4" t="s">
         <v>3</v>
@@ -2197,22 +2194,22 @@
         <v>3</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF10" s="4" t="s">
         <v>3</v>
@@ -2227,16 +2224,16 @@
         <v>2</v>
       </c>
       <c r="AJ10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL10" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AM10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN10" s="4" t="s">
         <v>3</v>
@@ -2254,13 +2251,13 @@
         <v>2</v>
       </c>
       <c r="AS10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV10" s="4" t="s">
         <v>3</v>
@@ -2269,7 +2266,7 @@
         <v>2</v>
       </c>
       <c r="AX10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY10" s="4" t="s">
         <v>3</v>
@@ -2280,7 +2277,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
@@ -2289,22 +2286,22 @@
         <v>3</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>2</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>2</v>
@@ -2313,7 +2310,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>3</v>
@@ -2322,7 +2319,7 @@
         <v>3</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>3</v>
@@ -2331,10 +2328,10 @@
         <v>2</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U11" s="4" t="s">
         <v>2</v>
@@ -2349,25 +2346,25 @@
         <v>3</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" s="4" t="s">
         <v>3</v>
@@ -2376,22 +2373,22 @@
         <v>2</v>
       </c>
       <c r="AH11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN11" s="4" t="s">
         <v>3</v>
@@ -2400,10 +2397,10 @@
         <v>3</v>
       </c>
       <c r="AP11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11" s="4" t="s">
         <v>2</v>
@@ -2421,10 +2418,10 @@
         <v>3</v>
       </c>
       <c r="AW11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX11" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY11" s="4" t="s">
         <v>3</v>
@@ -2435,16 +2432,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>3</v>
@@ -2453,28 +2450,28 @@
         <v>3</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" s="4" t="s">
         <v>3</v>
@@ -2483,13 +2480,13 @@
         <v>3</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U12" s="4" t="s">
         <v>2</v>
@@ -2501,16 +2498,16 @@
         <v>3</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB12" s="4" t="s">
         <v>3</v>
@@ -2519,22 +2516,22 @@
         <v>3</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ12" s="4" t="s">
         <v>3</v>
@@ -2543,22 +2540,22 @@
         <v>3</v>
       </c>
       <c r="AL12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR12" s="4" t="s">
         <v>2</v>
@@ -2567,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="AT12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV12" s="4" t="s">
         <v>3</v>
@@ -2579,10 +2576,10 @@
         <v>3</v>
       </c>
       <c r="AX12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.3">
@@ -2593,7 +2590,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>2</v>
@@ -2602,19 +2599,19 @@
         <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>3</v>
@@ -2623,16 +2620,16 @@
         <v>3</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="4" t="s">
         <v>3</v>
@@ -2641,22 +2638,22 @@
         <v>3</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="4" t="s">
         <v>2</v>
@@ -2668,13 +2665,13 @@
         <v>2</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>2</v>
@@ -2686,10 +2683,10 @@
         <v>3</v>
       </c>
       <c r="AH13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ13" s="4" t="s">
         <v>3</v>
@@ -2707,28 +2704,28 @@
         <v>2</v>
       </c>
       <c r="AO13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AQ13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AU13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW13" s="4" t="s">
         <v>3</v>
@@ -2737,7 +2734,7 @@
         <v>2</v>
       </c>
       <c r="AY13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.3">
@@ -2745,55 +2742,55 @@
         <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S14" s="4" t="s">
         <v>3</v>
@@ -2802,37 +2799,37 @@
         <v>3</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" s="4" t="s">
         <v>3</v>
@@ -2841,7 +2838,7 @@
         <v>3</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="4" t="s">
         <v>3</v>
@@ -2856,7 +2853,7 @@
         <v>2</v>
       </c>
       <c r="AM14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN14" s="4" t="s">
         <v>2</v>
@@ -2865,25 +2862,25 @@
         <v>3</v>
       </c>
       <c r="AP14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AU14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW14" s="4" t="s">
         <v>3</v>
@@ -2900,7 +2897,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
@@ -2921,10 +2918,10 @@
         <v>3</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>2</v>
@@ -2933,7 +2930,7 @@
         <v>3</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>3</v>
@@ -2948,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" s="4" t="s">
         <v>3</v>
@@ -2972,7 +2969,7 @@
         <v>3</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA15" s="4" t="s">
         <v>3</v>
@@ -2996,7 +2993,7 @@
         <v>3</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" s="4" t="s">
         <v>3</v>
@@ -3008,31 +3005,31 @@
         <v>3</v>
       </c>
       <c r="AL15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AN15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AP15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AR15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT15" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU15" s="4" t="s">
         <v>3</v>
@@ -3044,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="AX15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY15" s="4" t="s">
         <v>3</v>
@@ -3058,16 +3055,16 @@
         <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>3</v>
@@ -3076,43 +3073,43 @@
         <v>3</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V16" s="4" t="s">
         <v>3</v>
@@ -3121,28 +3118,28 @@
         <v>3</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z16" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF16" s="4" t="s">
         <v>3</v>
@@ -3151,43 +3148,43 @@
         <v>3</v>
       </c>
       <c r="AH16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AK16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU16" s="4" t="s">
         <v>3</v>
@@ -3196,13 +3193,13 @@
         <v>3</v>
       </c>
       <c r="AW16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.3">
@@ -3210,19 +3207,19 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>3</v>
@@ -3231,7 +3228,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>2</v>
@@ -3240,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>2</v>
@@ -3249,25 +3246,25 @@
         <v>2</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>3</v>
@@ -3276,13 +3273,13 @@
         <v>3</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA17" s="4" t="s">
         <v>2</v>
@@ -3291,52 +3288,52 @@
         <v>2</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AM17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AQ17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS17" s="4" t="s">
         <v>2</v>
@@ -3351,13 +3348,13 @@
         <v>3</v>
       </c>
       <c r="AW17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.3">
@@ -3365,37 +3362,37 @@
         <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>2</v>
@@ -3404,64 +3401,64 @@
         <v>2</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AB18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AG18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="4" t="s">
         <v>2</v>
@@ -3470,49 +3467,49 @@
         <v>2</v>
       </c>
       <c r="AK18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AM18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AQ18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AT18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.3">
@@ -3520,154 +3517,154 @@
         <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AN19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AP19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AV19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.3">
@@ -3681,10 +3678,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>3</v>
@@ -3693,7 +3690,7 @@
         <v>3</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>3</v>
@@ -3702,7 +3699,7 @@
         <v>3</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>3</v>
@@ -3717,13 +3714,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S20" s="4" t="s">
         <v>3</v>
@@ -3741,34 +3738,34 @@
         <v>3</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH20" s="4" t="s">
         <v>3</v>
@@ -3777,7 +3774,7 @@
         <v>3</v>
       </c>
       <c r="AJ20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK20" s="4" t="s">
         <v>3</v>
@@ -3786,19 +3783,19 @@
         <v>3</v>
       </c>
       <c r="AM20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AO20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AQ20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR20" s="4" t="s">
         <v>3</v>
@@ -3810,7 +3807,7 @@
         <v>3</v>
       </c>
       <c r="AU20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV20" s="4" t="s">
         <v>3</v>
@@ -3833,16 +3830,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>3</v>
@@ -3854,7 +3851,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>3</v>
@@ -3869,7 +3866,7 @@
         <v>3</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4" t="s">
         <v>3</v>
@@ -3878,28 +3875,28 @@
         <v>3</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21" s="4" t="s">
         <v>3</v>
@@ -3908,16 +3905,16 @@
         <v>3</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="4" t="s">
         <v>3</v>
@@ -3932,10 +3929,10 @@
         <v>3</v>
       </c>
       <c r="AJ21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL21" s="4" t="s">
         <v>3</v>
@@ -3944,16 +3941,16 @@
         <v>3</v>
       </c>
       <c r="AN21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR21" s="4" t="s">
         <v>3</v>
@@ -3962,10 +3959,10 @@
         <v>3</v>
       </c>
       <c r="AT21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV21" s="4" t="s">
         <v>3</v>
@@ -3977,7 +3974,7 @@
         <v>3</v>
       </c>
       <c r="AY21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.3">
@@ -3985,7 +3982,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>2</v>
@@ -3997,7 +3994,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>3</v>
@@ -4009,25 +4006,25 @@
         <v>3</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="s">
         <v>3</v>
@@ -4036,7 +4033,7 @@
         <v>3</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T22" s="4" t="s">
         <v>2</v>
@@ -4051,16 +4048,16 @@
         <v>2</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB22" s="4" t="s">
         <v>2</v>
@@ -4072,7 +4069,7 @@
         <v>3</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" s="4" t="s">
         <v>3</v>
@@ -4093,10 +4090,10 @@
         <v>2</v>
       </c>
       <c r="AL22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN22" s="4" t="s">
         <v>2</v>
@@ -4105,16 +4102,16 @@
         <v>2</v>
       </c>
       <c r="AP22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AR22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT22" s="4" t="s">
         <v>2</v>
@@ -4123,16 +4120,16 @@
         <v>2</v>
       </c>
       <c r="AV22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.3">
@@ -4143,22 +4140,22 @@
         <v>2</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>3</v>
@@ -4170,19 +4167,19 @@
         <v>3</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="4" t="s">
         <v>3</v>
@@ -4191,19 +4188,19 @@
         <v>3</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X23" s="4" t="s">
         <v>3</v>
@@ -4215,34 +4212,34 @@
         <v>3</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AJ23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="4" t="s">
         <v>2</v>
@@ -4251,10 +4248,10 @@
         <v>2</v>
       </c>
       <c r="AM23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23" s="4" t="s">
         <v>2</v>
@@ -4263,31 +4260,31 @@
         <v>3</v>
       </c>
       <c r="AQ23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AT23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AV23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.3">
@@ -4298,13 +4295,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>3</v>
@@ -4328,13 +4325,13 @@
         <v>3</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" s="4" t="s">
         <v>3</v>
@@ -4361,13 +4358,13 @@
         <v>3</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA24" s="4" t="s">
         <v>3</v>
@@ -4397,43 +4394,43 @@
         <v>3</v>
       </c>
       <c r="AJ24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AO24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AQ24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AS24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AU24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW24" s="4" t="s">
         <v>3</v>
@@ -4456,19 +4453,19 @@
         <v>2</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>3</v>
@@ -4480,19 +4477,19 @@
         <v>3</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="s">
         <v>3</v>
@@ -4510,19 +4507,19 @@
         <v>3</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X25" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA25" s="4" t="s">
         <v>3</v>
@@ -4531,10 +4528,10 @@
         <v>3</v>
       </c>
       <c r="AC25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" s="4" t="s">
         <v>2</v>
@@ -4543,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="AG25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH25" s="4" t="s">
         <v>2</v>
@@ -4552,16 +4549,16 @@
         <v>3</v>
       </c>
       <c r="AJ25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AM25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN25" s="4" t="s">
         <v>3</v>
@@ -4585,16 +4582,16 @@
         <v>3</v>
       </c>
       <c r="AU25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV25" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AW25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY25" s="4" t="s">
         <v>2</v>
@@ -4605,16 +4602,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>3</v>
@@ -4635,19 +4632,19 @@
         <v>3</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="s">
         <v>3</v>
@@ -4665,13 +4662,13 @@
         <v>3</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26" s="4" t="s">
         <v>2</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="4" t="s">
         <v>2</v>
@@ -4686,13 +4683,13 @@
         <v>3</v>
       </c>
       <c r="AC26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" s="4" t="s">
         <v>3</v>
@@ -4701,16 +4698,16 @@
         <v>3</v>
       </c>
       <c r="AH26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AJ26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL26" s="4" t="s">
         <v>3</v>
@@ -4734,25 +4731,25 @@
         <v>3</v>
       </c>
       <c r="AS26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AU26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV26" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AW26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.3">
@@ -4760,19 +4757,19 @@
         <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>3</v>
@@ -4781,7 +4778,7 @@
         <v>3</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>3</v>
@@ -4790,19 +4787,19 @@
         <v>3</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="4" t="s">
         <v>3</v>
@@ -4817,7 +4814,7 @@
         <v>3</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V27" s="4" t="s">
         <v>3</v>
@@ -4826,28 +4823,28 @@
         <v>2</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF27" s="4" t="s">
         <v>3</v>
@@ -4865,31 +4862,31 @@
         <v>3</v>
       </c>
       <c r="AK27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AQ27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AS27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT27" s="4" t="s">
         <v>3</v>
@@ -4907,172 +4904,17 @@
         <v>3</v>
       </c>
       <c r="AY27" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="S28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="T28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="V28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="W28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AS28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AU28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AY28" s="4" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A28">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AY28">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Available">
+  <conditionalFormatting sqref="A1:AY27">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Available">
       <formula>NOT(ISERROR(SEARCH("Available",A1)))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A27">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="60" fitToWidth="2" orientation="landscape" r:id="rId1"/>
